--- a/DOCTORSKIN2 data.xlsx
+++ b/DOCTORSKIN2 data.xlsx
@@ -15,24 +15,26 @@
     <sheet name="Brands" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Products" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Vouchers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Bills" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Bought" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Carts" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Wishlists" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Feedbacks" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="RepFeedbacks" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Services" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ServicesDetails" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="BlogTypes" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="BlogDetails" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Banners" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Medias" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Bookings" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Patients" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Doctors" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Medicines" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Forgots" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Questions" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Campaigns" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CampaignVouchers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Bills" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Bought" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Carts" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Wishlists" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Feedbacks" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="RepFeedbacks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Services" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ServicesDetails" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="BlogTypes" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="BlogDetails" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Banners" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Medias" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Bookings" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Patients" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Doctors" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Medicines" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Forgots" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Questions" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +535,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0900000000</t>
+          <t>900000000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -583,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0939958838</t>
+          <t>939958838</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -633,7 +635,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0914265799</t>
+          <t>914265799</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -683,7 +685,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0997226012</t>
+          <t>997226012</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -733,7 +735,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0910872248</t>
+          <t>910872248</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -783,7 +785,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0930868105</t>
+          <t>930868105</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -833,7 +835,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0958181396</t>
+          <t>958181396</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -883,7 +885,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0960806024</t>
+          <t>960806024</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -933,7 +935,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0916150444</t>
+          <t>916150444</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -983,7 +985,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0923556182</t>
+          <t>923556182</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1033,7 +1035,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0957683626</t>
+          <t>957683626</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1083,7 +1085,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0931931511</t>
+          <t>931931511</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1133,7 +1135,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0917507864</t>
+          <t>917507864</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1183,7 +1185,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0918883684</t>
+          <t>918883684</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1233,7 +1235,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0963100814</t>
+          <t>963100814</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1283,7 +1285,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0985345555</t>
+          <t>985345555</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1333,7 +1335,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0958586340</t>
+          <t>958586340</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1383,7 +1385,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0924716857</t>
+          <t>924716857</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1433,7 +1435,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0961220073</t>
+          <t>961220073</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1483,7 +1485,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0982070937</t>
+          <t>982070937</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1533,7 +1535,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0968353204</t>
+          <t>968353204</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1583,7 +1585,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0993926371</t>
+          <t>993926371</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1633,7 +1635,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0931682744</t>
+          <t>931682744</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1683,7 +1685,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0912614124</t>
+          <t>912614124</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1733,7 +1735,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0942329237</t>
+          <t>942329237</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1783,7 +1785,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0927232410</t>
+          <t>927232410</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1833,7 +1835,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0938427073</t>
+          <t>938427073</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1883,7 +1885,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0968800797</t>
+          <t>968800797</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1933,7 +1935,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0955377076</t>
+          <t>955377076</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1983,7 +1985,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0919528530</t>
+          <t>919528530</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2033,7 +2035,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0954349361</t>
+          <t>954349361</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2066,23 +2068,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>stt</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>iduser</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>idp</t>
+          <t>voucher_id</t>
         </is>
       </c>
     </row>
@@ -2090,260 +2092,78 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>u021</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>20</v>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VC01</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>u011</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VC01</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>u027</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VC02</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>u022</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VC01</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>u008</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>7</v>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VC02</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>u005</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>u002</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>u016</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>u028</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>u015</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>u029</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>u007</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>u016</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>u008</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>u021</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>u029</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>u025</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>u008</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>u026</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>u015</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VC03</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2357,13 +2177,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>stt</t>
+          <t>sttbill</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2378,7 +2198,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>quanlity</t>
+          <t>totalmoney</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>datebuy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>idvoucher</t>
         </is>
       </c>
     </row>
@@ -2388,15 +2223,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>u018</t>
+          <t>u019</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1946000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2404,14 +2252,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>u015</t>
+          <t>u002</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>340000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VC02</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2424,11 +2289,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1366000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2440,11 +2318,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1058000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2452,14 +2343,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>u020</t>
+          <t>u019</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>17</v>
       </c>
-      <c r="D6" t="n">
-        <v>4</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>618000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VC03</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2468,14 +2376,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>u027</t>
+          <t>u008</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1136000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VC03</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2484,15 +2409,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>u029</t>
+          <t>u001</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1353000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2500,15 +2438,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>u015</t>
+          <t>u018</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>471000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2516,14 +2467,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>u027</t>
+          <t>u029</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1097000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VC02</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2532,15 +2500,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>u016</t>
+          <t>u010</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1852000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2548,14 +2529,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>u015</t>
+          <t>u001</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1998000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>VC01</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2564,15 +2562,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>u008</t>
+          <t>u004</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>518000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2580,15 +2591,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>u011</t>
+          <t>u020</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>616000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2596,15 +2620,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>u005</t>
+          <t>u028</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>714000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2612,15 +2649,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>u013</t>
+          <t>u021</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>290000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2628,15 +2678,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>u003</t>
+          <t>u025</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>736000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2644,15 +2707,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>u011</t>
+          <t>u018</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>429000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2660,15 +2736,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>u014</t>
+          <t>u029</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1909000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2676,15 +2765,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>u027</t>
+          <t>u018</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>285000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2696,10 +2798,668 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
-      </c>
-      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>630000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>u022</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1991000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>u024</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>684000</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>u029</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>14</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1802000</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>u028</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>983000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>u008</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1142000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>u027</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1016000</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>u028</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>771000</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>u017</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1927000</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>u001</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>734000</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>u009</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>907000</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>u014</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>436000</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>u007</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>203000</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>u022</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1560000</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>u011</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>815000</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>u022</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1335000</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>VC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>u014</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>13</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>556000</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>u010</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>u007</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1442000</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>u015</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>15</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>637000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>u026</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>781000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>u002</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
         <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>308700</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Chờ thanh toán</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>VC01</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2739,11 +3499,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>u028</t>
+          <t>u021</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2752,11 +3512,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>u013</t>
+          <t>u011</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2765,11 +3525,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>u001</t>
+          <t>u027</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2778,11 +3538,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>u010</t>
+          <t>u022</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2791,11 +3551,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>u028</t>
+          <t>u008</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2804,11 +3564,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>u018</t>
+          <t>u005</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2817,11 +3577,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>u026</t>
+          <t>u002</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2830,11 +3590,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>u029</t>
+          <t>u016</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -2843,11 +3603,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>u016</t>
+          <t>u028</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2856,7 +3616,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>u009</t>
+          <t>u015</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2869,11 +3629,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>u016</t>
+          <t>u029</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -2882,11 +3642,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>u013</t>
+          <t>u007</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -2895,7 +3655,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>u022</t>
+          <t>u016</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2908,11 +3668,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>u024</t>
+          <t>u008</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2921,11 +3681,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>u027</t>
+          <t>u021</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2934,11 +3694,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>u030</t>
+          <t>u029</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2947,11 +3707,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>u020</t>
+          <t>u025</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2960,11 +3720,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>u001</t>
+          <t>u008</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2973,11 +3733,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>u019</t>
+          <t>u026</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2986,11 +3746,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>u022</t>
+          <t>u015</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3004,13 +3764,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sttfb</t>
+          <t>stt</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -3025,22 +3785,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>cmt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>star</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>img</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>datefb</t>
+          <t>quanlity</t>
         </is>
       </c>
     </row>
@@ -3050,25 +3795,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>u003</t>
+          <t>u018</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Feedback 1</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3077,25 +3811,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>u006</t>
+          <t>u015</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Feedback 2</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -3104,25 +3827,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>u011</t>
+          <t>u022</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Feedback 3</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2025-10-22</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -3131,25 +3843,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>u011</t>
+          <t>u020</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Feedback 4</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3158,25 +3859,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>u009</t>
+          <t>u020</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Feedback 5</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3185,25 +3875,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>u024</t>
+          <t>u027</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>18</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Feedback 6</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
+      <c r="D7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3212,25 +3891,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>u008</t>
+          <t>u029</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Feedback 7</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3239,25 +3907,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>u025</t>
+          <t>u015</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Feedback 8</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3270,21 +3927,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Feedback 9</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
         <v>5</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -3293,25 +3939,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>u008</t>
+          <t>u016</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Feedback 10</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2025-07-26</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3320,25 +3955,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>u004</t>
+          <t>u015</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Feedback 11</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
+      <c r="D12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3347,25 +3971,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>u023</t>
+          <t>u008</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Feedback 12</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
+      <c r="D13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3374,25 +3987,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>u020</t>
+          <t>u011</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Feedback 13</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3401,25 +4003,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>u025</t>
+          <t>u005</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Feedback 14</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -3428,25 +4019,126 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>u019</t>
+          <t>u013</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>u003</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>u011</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>u014</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>u027</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>u029</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Feedback 15</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>u017</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>u010</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3460,7 +4152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3471,17 +4163,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sttfb</t>
+          <t>iduser</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>contentrep</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>daterep</t>
+          <t>idp</t>
         </is>
       </c>
     </row>
@@ -3489,180 +4176,260 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Reply 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>u028</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Reply 2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>u013</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Reply 3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
-        </is>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>u001</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Reply 4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>u010</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Reply 5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>u028</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Reply 6</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>u018</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Reply 7</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>u026</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Reply 8</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>u029</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>13</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Reply 9</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>u016</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>u009</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>u016</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>u013</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Reply 10</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>u022</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>u024</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>u027</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>u030</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>u020</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>u001</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>u019</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>u022</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3676,28 +4443,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id_dt</t>
+          <t>sttfb</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name_dt</t>
+          <t>iduser</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>desc_dt</t>
+          <t>idp</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>img_dt</t>
+          <t>cmt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>img</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>datefb</t>
         </is>
       </c>
     </row>
@@ -3707,15 +4489,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Service 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Description 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>u003</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Feedback 1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3723,15 +4516,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Service 2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Description 2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>u006</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Feedback 2</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3739,15 +4543,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Service 3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Description 3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>u011</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Feedback 3</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3755,15 +4570,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Service 4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Description 4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>u011</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Feedback 4</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3771,15 +4597,296 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Service 5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Description 5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>u009</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Feedback 5</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>u024</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Feedback 6</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>u008</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Feedback 7</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>u025</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Feedback 8</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>u027</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Feedback 9</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>u008</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Feedback 10</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>u004</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Feedback 11</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>u023</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Feedback 12</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>u020</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Feedback 13</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>u025</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Feedback 14</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>u019</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Feedback 15</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3798,22 +4905,22 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id_sd</t>
+          <t>stt</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>id_dt</t>
+          <t>sttfb</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>name_sd</t>
+          <t>contentrep</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>price_sd</t>
+          <t>daterep</t>
         </is>
       </c>
     </row>
@@ -3822,16 +4929,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Service 1 - Package 1</t>
+          <t>Reply 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>555000</t>
+          <t>2025-10-09</t>
         </is>
       </c>
     </row>
@@ -3840,16 +4947,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Service 1 - Package 2</t>
+          <t>Reply 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>745000</t>
+          <t>2025-11-24</t>
         </is>
       </c>
     </row>
@@ -3862,12 +4969,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Service 2 - Package 1</t>
+          <t>Reply 3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>638000</t>
+          <t>2025-08-15</t>
         </is>
       </c>
     </row>
@@ -3876,16 +4983,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service 2 - Package 2</t>
+          <t>Reply 4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>877000</t>
+          <t>2025-08-06</t>
         </is>
       </c>
     </row>
@@ -3894,16 +5001,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Service 3 - Package 1</t>
+          <t>Reply 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>579000</t>
+          <t>2025-12-18</t>
         </is>
       </c>
     </row>
@@ -3912,16 +5019,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Service 3 - Package 2</t>
+          <t>Reply 6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>270000</t>
+          <t>2025-10-28</t>
         </is>
       </c>
     </row>
@@ -3930,16 +5037,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Service 4 - Package 1</t>
+          <t>Reply 7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>718000</t>
+          <t>2025-07-22</t>
         </is>
       </c>
     </row>
@@ -3948,16 +5055,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Service 4 - Package 2</t>
+          <t>Reply 8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>863000</t>
+          <t>2025-12-14</t>
         </is>
       </c>
     </row>
@@ -3966,16 +5073,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Service 5 - Package 1</t>
+          <t>Reply 9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>549000</t>
+          <t>2025-08-22</t>
         </is>
       </c>
     </row>
@@ -3984,16 +5091,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Service 5 - Package 2</t>
+          <t>Reply 10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>212000</t>
+          <t>2026-01-03</t>
         </is>
       </c>
     </row>
@@ -4008,18 +5115,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>idbt</t>
+          <t>id_dt</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>namebt</t>
+          <t>name_dt</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>desc_dt</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>img_dt</t>
         </is>
       </c>
     </row>
@@ -4029,9 +5146,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blog type 1</t>
-        </is>
-      </c>
+          <t>Điều trị mụn chuyên sâu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Description 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4039,9 +5162,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blog type 2</t>
-        </is>
-      </c>
+          <t>Chăm sóc da cơ bản</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Description 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4049,9 +5178,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blog type 3</t>
-        </is>
-      </c>
+          <t>Trị nám công nghệ cao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Description 3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Peel da sinh học</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Description 4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Làm sạch da y khoa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Description 5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4064,43 +5231,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>idb</t>
+          <t>id_sd</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>idbt</t>
+          <t>id_dt</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>name_sd</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>contentblog</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>img</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>hide</t>
+          <t>price_sd</t>
         </is>
       </c>
     </row>
@@ -4109,26 +5261,17 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Blog 1</t>
+          <t>Gói cơ bản</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>blog-1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>0</v>
+          <t>555000</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4136,26 +5279,17 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Blog 2</t>
+          <t>Gói nâng cao</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>blog-2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>0</v>
+          <t>745000</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4163,26 +5297,17 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Blog 3</t>
+          <t>Gói chuyên sâu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>blog-3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>0</v>
+          <t>638000</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4194,22 +5319,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Blog 4</t>
+          <t>Gói phục hồi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>blog-4</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>0</v>
+          <t>877000</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4217,26 +5333,107 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blog 5</t>
+          <t>Gói VIP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>blog-5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>0</v>
+          <t>579000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gói cơ bản</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>270000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Gói nâng cao</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>718000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gói chuyên sâu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>863000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gói phục hồi</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>549000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gói VIP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>212000</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4250,38 +5447,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>stt</t>
+          <t>idbt</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>homepage</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>servicepage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>blogpage</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>productpage</t>
+          <t>namebt</t>
         </is>
       </c>
     </row>
@@ -4291,20 +5468,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://example.com/banner/1.png</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
+          <t>Blog type 1</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4313,20 +5478,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://example.com/banner/2.png</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
+          <t>Blog type 2</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4335,20 +5488,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://example.com/banner/3.png</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
+          <t>Blog type 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4956,18 +6097,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>stt</t>
+          <t>idb</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>idbt</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>contentblog</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>img</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>hide</t>
         </is>
       </c>
     </row>
@@ -4975,50 +6141,135 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://example.com/media/1.png</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Blog 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>blog-1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://example.com/media/2.png</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Blog 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>blog-2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://example.com/media/3.png</t>
-        </is>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Blog 3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>blog-3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://example.com/media/4.png</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Blog 4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>blog-4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://example.com/media/5.png</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Blog 5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>blog-5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5032,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5043,22 +6294,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>link</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>homepage</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>timebooking</t>
+          <t>servicepage</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>require</t>
+          <t>blogpage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>productpage</t>
         </is>
       </c>
     </row>
@@ -5068,23 +6324,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ngo Bao Chau</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0971705170</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Request 1</t>
-        </is>
+          <t>https://example.com/banner/1.png</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5093,23 +6346,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vu Hoang Long</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0933640702</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Request 2</t>
-        </is>
+          <t>https://example.com/banner/2.png</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5118,448 +6368,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ngo Bao Chau</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0946249845</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Request 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pham Minh Quang</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0982232344</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Request 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bui Tuyet Mai</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0968461818</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Request 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hoang Gia Bao</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0953258988</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Request 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Le Thu Ha</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0921631697</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Request 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nguyen Thi Lan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0970505620</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Request 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Pham Minh Quang</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0972372114</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Request 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dang Thuy Chi</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0999682738</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Request 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Do Quoc Anh</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0913852048</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Request 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Le Thu Ha</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0953622663</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Request 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bui Tuyet Mai</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0938470244</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Request 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Pham Minh Quang</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0944675473</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Request 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Hoang Gia Bao</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0990014570</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Request 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nguyen Thi Lan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0947080140</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Request 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Nguyen Van An</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0979340535</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Request 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Le Thi Binh</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0942394260</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Request 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Bui Tuyet Mai</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0984514489</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Request 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tran Quang Kiet</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0973900135</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Request 20</t>
-        </is>
+          <t>https://example.com/banner/3.png</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5573,7 +6395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5584,42 +6406,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>diagnose</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>prescription</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>date_re</t>
+          <t>link</t>
         </is>
       </c>
     </row>
@@ -5629,42 +6416,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tran Quang Kiet</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0975876924</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Quan Tay Ho, Ha Noi</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Diagnose 1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Prescription 1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
+          <t>https://example.com/media/1.png</t>
         </is>
       </c>
     </row>
@@ -5674,42 +6426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pham Thanh Dieu</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0964277800</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Quan Phu Nhuan, TP.HCM</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Diagnose 2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Prescription 2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Le Thi Binh</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
+          <t>https://example.com/media/2.png</t>
         </is>
       </c>
     </row>
@@ -5719,42 +6436,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Do Quoc Anh</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0973519947</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ninh Kieu, Can Tho</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Diagnose 3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Prescription 3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Le Thi Binh</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
+          <t>https://example.com/media/3.png</t>
         </is>
       </c>
     </row>
@@ -5764,42 +6446,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Do Quoc Anh</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0970900658</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hai Chau, Da Nang</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Diagnose 4</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Prescription 4</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Le Thi Binh</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
+          <t>https://example.com/media/4.png</t>
         </is>
       </c>
     </row>
@@ -5809,492 +6456,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Le Thi Binh</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0935848226</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ninh Kieu, Can Tho</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Diagnose 5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Prescription 5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Tran Minh Cuong</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0935708194</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Quan Phu Nhuan, TP.HCM</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Diagnose 6</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Prescription 6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Ngo Bao Chau</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Tran Quang Kiet</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0989133014</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Hai Chau, Da Nang</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Diagnose 7</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Prescription 7</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Pham Thanh Dieu</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0958436637</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Quan 7, TP.HCM</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Diagnose 8</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Prescription 8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Le Thi Binh</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tran Minh Cuong</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0946817443</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Quan 1, TP.HCM</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Diagnose 9</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Prescription 9</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tran Quang Kiet</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0926948946</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Quan Tay Ho, Ha Noi</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Diagnose 10</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Prescription 10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hoang Gia Bao</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0973001391</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Quan Tay Ho, Ha Noi</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Diagnose 11</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Prescription 11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Le Thi Binh</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nguyen Van An</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0943887075</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Quan Tay Ho, Ha Noi</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Diagnose 12</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Prescription 12</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bui Tuyet Mai</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0919943140</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Quan 1, TP.HCM</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Diagnose 13</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Prescription 13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hoang Gia Bao</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0921432787</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Quan Phu Nhuan, TP.HCM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Diagnose 14</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Prescription 14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dang Thuy Chi</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0990010790</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Quan Phu Nhuan, TP.HCM</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Diagnose 15</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Prescription 15</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Ngo Bao Chau</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
+          <t>https://example.com/media/5.png</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6320,17 +6482,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>namedoc</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>iddoc</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>infordoc</t>
+          <t>timebooking</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>require</t>
         </is>
       </c>
     </row>
@@ -6340,17 +6507,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Le Thi Binh</t>
+          <t>Ngo Bao Chau</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>u001</t>
+          <t>971705170</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Specialist 1</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Request 1</t>
         </is>
       </c>
     </row>
@@ -6360,17 +6532,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ngo Bao Chau</t>
+          <t>Vu Hoang Long</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>u002</t>
+          <t>933640702</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Specialist 2</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Request 2</t>
         </is>
       </c>
     </row>
@@ -6380,19 +6557,470 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pham Thanh Dieu</t>
+          <t>Ngo Bao Chau</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>u003</t>
+          <t>946249845</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Specialist 3</t>
-        </is>
-      </c>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Request 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pham Minh Quang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>982232344</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Request 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bui Tuyet Mai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>968461818</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Request 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hoang Gia Bao</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>953258988</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Request 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Le Thu Ha</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>921631697</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Request 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nguyen Thi Lan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>970505620</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Request 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pham Minh Quang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>972372114</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Request 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dang Thuy Chi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>999682738</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Request 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Do Quoc Anh</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>913852048</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Request 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Le Thu Ha</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>953622663</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Request 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bui Tuyet Mai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>938470244</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Request 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pham Minh Quang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>944675473</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Request 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hoang Gia Bao</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>990014570</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Request 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nguyen Thi Lan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>947080140</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Request 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nguyen Van An</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>979340535</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Request 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Le Thi Binh</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>942394260</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Request 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bui Tuyet Mai</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>984514489</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Request 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tran Quang Kiet</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>973900135</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Request 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-01-13T20:02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6405,13 +7033,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>stt</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -6421,17 +7049,37 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>uses</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>hide</t>
+          <t>diagnose</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>prescription</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>date_re</t>
         </is>
       </c>
     </row>
@@ -6441,21 +7089,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Medicine 1</t>
+          <t>Tran Quang Kiet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>282000</t>
+          <t>975876924</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
+          <t>Quan Tay Ho, Ha Noi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Diagnose 1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Prescription 1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -6464,21 +7134,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medicine 2</t>
+          <t>Pham Thanh Dieu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>163000</t>
+          <t>964277800</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
+          <t>Quan Phu Nhuan, TP.HCM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Diagnose 2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Prescription 2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Le Thi Binh</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -6487,21 +7179,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Medicine 3</t>
+          <t>Do Quoc Anh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>126000</t>
+          <t>973519947</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
+          <t>Ninh Kieu, Can Tho</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Diagnose 3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Prescription 3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Le Thi Binh</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -6510,21 +7224,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Medicine 4</t>
+          <t>Do Quoc Anh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>270000</t>
+          <t>970900658</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
+          <t>Hai Chau, Da Nang</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Diagnose 4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prescription 4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Le Thi Binh</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -6533,21 +7269,493 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Medicine 5</t>
+          <t>Le Thi Binh</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>935848226</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
+          <t>Ninh Kieu, Can Tho</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Diagnose 5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Prescription 5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tran Minh Cuong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>935708194</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quan Phu Nhuan, TP.HCM</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Diagnose 6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Prescription 6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ngo Bao Chau</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tran Quang Kiet</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>989133014</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hai Chau, Da Nang</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Diagnose 7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Prescription 7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pham Thanh Dieu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>958436637</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quan 7, TP.HCM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Diagnose 8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Prescription 8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Le Thi Binh</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tran Minh Cuong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>946817443</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quan 1, TP.HCM</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Diagnose 9</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Prescription 9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tran Quang Kiet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>926948946</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quan Tay Ho, Ha Noi</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Diagnose 10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Prescription 10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hoang Gia Bao</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>973001391</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quan Tay Ho, Ha Noi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Diagnose 11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Prescription 11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Le Thi Binh</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nguyen Van An</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>943887075</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quan Tay Ho, Ha Noi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Diagnose 12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Prescription 12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bui Tuyet Mai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>919943140</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quan 1, TP.HCM</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Diagnose 13</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Prescription 13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hoang Gia Bao</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>921432787</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quan Phu Nhuan, TP.HCM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Diagnose 14</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Prescription 14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dang Thuy Chi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>990010790</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Quan Phu Nhuan, TP.HCM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Diagnose 15</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Prescription 15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ngo Bao Chau</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6561,7 +7769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6572,17 +7780,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>namedoc</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>iddoc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>infordoc</t>
         </is>
       </c>
     </row>
@@ -6592,17 +7800,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>user014@mail.com</t>
+          <t>Le Thi Binh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>token1</t>
+          <t>u001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>Specialist 1</t>
         </is>
       </c>
     </row>
@@ -6612,17 +7820,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user019@mail.com</t>
+          <t>Ngo Bao Chau</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>token2</t>
+          <t>u002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>Specialist 2</t>
         </is>
       </c>
     </row>
@@ -6632,57 +7840,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user002@mail.com</t>
+          <t>Pham Thanh Dieu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>token3</t>
+          <t>u003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>user024@mail.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>token4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>user025@mail.com</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>token5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
+          <t>Specialist 3</t>
         </is>
       </c>
     </row>
@@ -6692,6 +7860,298 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>uses</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medicine 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>282000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Medicine 2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>163000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Medicine 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>126000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Medicine 4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>270000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Medicine 5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>stt</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>user014@mail.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>token1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>user019@mail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>token2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>user002@mail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>token3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>user024@mail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>token4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>user025@mail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>token5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7591,7 +9051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Product 1</t>
+          <t>Sữa rửa mặt dịu nhẹ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7630,7 +9090,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Product 2</t>
+          <t>Toner cân bằng da</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7669,7 +9129,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Product 3</t>
+          <t>Serum Vitamin C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7708,7 +9168,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Product 4</t>
+          <t>Kem chống nắng phổ rộng</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7747,7 +9207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Product 5</t>
+          <t>Kem dưỡng ẩm phục hồi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7786,7 +9246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Product 6</t>
+          <t>Mặt nạ dưỡng sáng</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7825,7 +9285,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Product 7</t>
+          <t>Tẩy tế bào chết AHA/BHA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7864,7 +9324,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Product 8</t>
+          <t>Gel trị mụn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7903,7 +9363,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Product 9</t>
+          <t>Tinh chất HA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7942,7 +9402,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Product 10</t>
+          <t>Kem mắt giảm quầng</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7981,7 +9441,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Product 11</t>
+          <t>Xịt khoáng cấp ẩm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8020,7 +9480,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Product 12</t>
+          <t>Sữa rửa mặt cho da dầu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8059,7 +9519,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Product 13</t>
+          <t>Serum retinol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8098,7 +9558,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Product 14</t>
+          <t>Kem dưỡng ban đêm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8137,7 +9597,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Product 15</t>
+          <t>Mặt nạ đất sét</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8176,7 +9636,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Product 16</t>
+          <t>Sữa rửa mặt dịu nhẹ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8215,7 +9675,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Product 17</t>
+          <t>Toner cân bằng da</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8254,7 +9714,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Product 18</t>
+          <t>Serum Vitamin C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8293,7 +9753,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Product 19</t>
+          <t>Kem chống nắng phổ rộng</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8332,7 +9792,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Product 20</t>
+          <t>Kem dưỡng ẩm phục hồi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8542,43 +10002,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sttbill</t>
+          <t>id_campaign</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>iduser</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>idp</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>totalmoney</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>datebuy</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>idvoucher</t>
         </is>
       </c>
     </row>
@@ -8588,28 +10043,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>u019</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>16</v>
+          <t>Khuyến mãi mùa hè</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Giảm giá dịch vụ chăm sóc da</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1946000</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Đang chạy</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -8617,30 +10073,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>u002</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>17</v>
+          <t>Tri ân khách hàng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tặng voucher cho khách thân thiết</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>340000</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>VC02</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
@@ -8650,1149 +10103,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>u022</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
+          <t>Sự kiện cuối năm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ưu đãi combo điều trị</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1366000</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>u020</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1058000</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>u019</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>17</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>618000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>u008</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1136000</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>u001</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1353000</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>u018</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>471000</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>u029</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1097000</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VC02</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>u010</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>20</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1852000</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>u001</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1998000</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>VC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>u004</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>518000</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>u020</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>616000</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>u028</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>714000</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>u021</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>290000</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2025-10-20</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>u025</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>736000</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>u018</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>14</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>429000</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>u029</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1909000</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>u018</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>285000</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>u029</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>630000</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>u022</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1991000</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VC05</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>u024</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>684000</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>u029</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>14</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1802000</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>VC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>u028</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>983000</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>u008</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1142000</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>u027</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1016000</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VC02</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>u028</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>771000</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>u017</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>13</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1927000</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>u001</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>734000</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>u009</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>907000</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>VC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>u014</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>20</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>436000</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>u007</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>9</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>203000</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>VC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>u022</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1560000</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>VC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>u011</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>815000</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>u022</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>14</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1335000</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>VC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>u014</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>556000</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>u010</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>13</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>u007</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>14</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1442000</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>u015</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>15</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>637000</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>u026</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>6</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>781000</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Kết thúc</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
